--- a/src/nodes/LPC/compresor_blade_self_frequency.xlsx
+++ b/src/nodes/LPC/compresor_blade_self_frequency.xlsx
@@ -552,58 +552,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>188.813208049794</v>
+        <v>152.05526270493061</v>
       </c>
       <c r="C3">
-        <v>1183.3575816992513</v>
+        <v>952.98284382572547</v>
       </c>
       <c r="D3">
-        <v>3313.7688093043325</v>
+        <v>2668.6479830865051</v>
       </c>
       <c r="E3">
-        <v>6498.5310361671327</v>
+        <v>5233.4042417199234</v>
       </c>
       <c r="F3">
-        <v>10738.129718668117</v>
+        <v>8647.6425679982221</v>
       </c>
       <c r="G3">
-        <v>16036.784873965686</v>
+        <v>12914.761430832912</v>
       </c>
       <c r="H3">
-        <v>692.78770795260687</v>
+        <v>519.78451907992053</v>
       </c>
       <c r="I3">
-        <v>2078.3631238578209</v>
+        <v>1559.3535572397616</v>
       </c>
       <c r="J3">
-        <v>3463.9385397630344</v>
+        <v>2598.9225953996024</v>
       </c>
       <c r="K3">
-        <v>4849.5139556682479</v>
+        <v>3638.4916335594435</v>
       </c>
       <c r="L3">
-        <v>6235.0893715734619</v>
+        <v>4678.060671719285</v>
       </c>
       <c r="M3">
-        <v>7620.664787478675</v>
+        <v>5717.6297098791256</v>
       </c>
       <c r="N3">
-        <v>1385.5754159052137</v>
+        <v>1039.5690381598411</v>
       </c>
       <c r="O3">
-        <v>2771.1508318104275</v>
+        <v>2079.1380763196821</v>
       </c>
       <c r="P3">
-        <v>4156.7262477156419</v>
+        <v>3118.7071144795232</v>
       </c>
       <c r="Q3">
-        <v>5542.3016636208549</v>
+        <v>4158.2761526393642</v>
       </c>
       <c r="R3">
-        <v>6927.8770795260689</v>
+        <v>5197.8451907992048</v>
       </c>
       <c r="S3">
-        <v>8313.4524954312838</v>
+        <v>6237.4142289590463</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -611,58 +611,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>258.78706261871679</v>
+        <v>228.06177892662055</v>
       </c>
       <c r="C4">
-        <v>1621.9078938311147</v>
+        <v>1429.3419299218851</v>
       </c>
       <c r="D4">
-        <v>4541.8459080004313</v>
+        <v>4002.6013932361643</v>
       </c>
       <c r="E4">
-        <v>8906.8756129748581</v>
+        <v>7849.3796267011094</v>
       </c>
       <c r="F4">
-        <v>14717.662374445852</v>
+        <v>12970.262998436108</v>
       </c>
       <c r="G4">
-        <v>21979.990140771173</v>
+        <v>19370.348739880566</v>
       </c>
       <c r="H4">
-        <v>700.0822101617016</v>
+        <v>525.2571832967709</v>
       </c>
       <c r="I4">
-        <v>2100.246630485105</v>
+        <v>1575.7715498903128</v>
       </c>
       <c r="J4">
-        <v>3500.4110508085082</v>
+        <v>2626.2859164838542</v>
       </c>
       <c r="K4">
-        <v>4900.5754711319123</v>
+        <v>3676.8002830773967</v>
       </c>
       <c r="L4">
-        <v>6300.739891455316</v>
+        <v>4727.3146496709387</v>
       </c>
       <c r="M4">
-        <v>7700.9043117787178</v>
+        <v>5777.82901626448</v>
       </c>
       <c r="N4">
-        <v>1400.1644203234032</v>
+        <v>1050.5143665935418</v>
       </c>
       <c r="O4">
-        <v>2800.3288406468064</v>
+        <v>2101.0287331870836</v>
       </c>
       <c r="P4">
-        <v>4200.49326097021</v>
+        <v>3151.5430997806257</v>
       </c>
       <c r="Q4">
-        <v>5600.6576812936128</v>
+        <v>4202.0574663741672</v>
       </c>
       <c r="R4">
-        <v>7000.8221016170164</v>
+        <v>5252.5718329677084</v>
       </c>
       <c r="S4">
-        <v>8400.98652194042</v>
+        <v>6303.0861995612513</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -670,58 +670,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>255.19148742697348</v>
+        <v>220.56702553508018</v>
       </c>
       <c r="C5">
-        <v>1599.3731823685716</v>
+        <v>1382.3697220956906</v>
       </c>
       <c r="D5">
-        <v>4478.7417160587038</v>
+        <v>3871.0646205768885</v>
       </c>
       <c r="E5">
-        <v>8783.1239050421445</v>
+        <v>7591.4268699718259</v>
       </c>
       <c r="F5">
-        <v>14513.175870450948</v>
+        <v>12544.023568689416</v>
       </c>
       <c r="G5">
-        <v>21674.601198738321</v>
+        <v>18733.784438765255</v>
       </c>
       <c r="H5">
-        <v>674.80346593371519</v>
+        <v>506.29114303980555</v>
       </c>
       <c r="I5">
-        <v>2024.4103978011456</v>
+        <v>1518.8734291194166</v>
       </c>
       <c r="J5">
-        <v>3374.0173296685757</v>
+        <v>2531.455715199028</v>
       </c>
       <c r="K5">
-        <v>4723.624261536007</v>
+        <v>3544.0380012786391</v>
       </c>
       <c r="L5">
-        <v>6073.2311934034369</v>
+        <v>4556.6202873582506</v>
       </c>
       <c r="M5">
-        <v>7422.8381252708677</v>
+        <v>5569.2025734378622</v>
       </c>
       <c r="N5">
-        <v>1349.6069318674304</v>
+        <v>1012.5822860796111</v>
       </c>
       <c r="O5">
-        <v>2699.2138637348608</v>
+        <v>2025.1645721592222</v>
       </c>
       <c r="P5">
-        <v>4048.8207956022911</v>
+        <v>3037.7468582388333</v>
       </c>
       <c r="Q5">
-        <v>5398.4277274697215</v>
+        <v>4050.3291443184444</v>
       </c>
       <c r="R5">
-        <v>6748.0346593371514</v>
+        <v>5062.9114303980559</v>
       </c>
       <c r="S5">
-        <v>8097.6415912045823</v>
+        <v>6075.4937164776666</v>
       </c>
     </row>
   </sheetData>
